--- a/Assets/TableDate/CardConfig.xlsx
+++ b/Assets/TableDate/CardConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity\Kill Kard\Assets\TableDate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C1CDE6-68EE-49DD-B2F0-962703E8BF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B1DD4C-FFAD-4AFA-BCEE-5D6046C42D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1395" yWindow="855" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3885" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardConfig" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>id</t>
   </si>
@@ -39,18 +39,9 @@
     <t>type</t>
   </si>
   <si>
-    <t>buff</t>
-  </si>
-  <si>
     <t>number</t>
   </si>
   <si>
-    <t>buffnumber</t>
-  </si>
-  <si>
-    <t>livenumber</t>
-  </si>
-  <si>
     <t>sprite</t>
   </si>
   <si>
@@ -66,62 +57,69 @@
     <t>卡牌类型(CardType枚举)</t>
   </si>
   <si>
-    <t>Buff类型(CardBuff枚举)</t>
-  </si>
-  <si>
     <t>卡牌基础数值</t>
   </si>
   <si>
-    <t>Buff效果数值</t>
-  </si>
-  <si>
-    <t>存在回合数</t>
-  </si>
-  <si>
     <t>卡牌图片资源路径</t>
   </si>
   <si>
     <t>Basic Strike</t>
   </si>
   <si>
-    <t>造成 10 点伤害</t>
-  </si>
-  <si>
     <t>Healing Potion</t>
   </si>
   <si>
-    <t>恢复 15 点生命值</t>
-  </si>
-  <si>
     <t>Shield Ward</t>
   </si>
   <si>
-    <t>获得 8 点护盾</t>
-  </si>
-  <si>
     <t>Power Up</t>
   </si>
   <si>
-    <t>攻击力 + 5，持续 3 回合</t>
-  </si>
-  <si>
     <t>Iron Skin</t>
   </si>
   <si>
-    <t>防御力 + 3，持续 2 回合</t>
-  </si>
-  <si>
     <t>Furious Blow</t>
   </si>
   <si>
-    <t>造成 12 点伤害，攻击力 + 2，持续 1 回合</t>
+    <t>Deal 10 damage</t>
+  </si>
+  <si>
+    <t>Restore 15 HP</t>
+  </si>
+  <si>
+    <t>Gain 8 shield</t>
+  </si>
+  <si>
+    <t>Attack +5 for 3 turns</t>
+  </si>
+  <si>
+    <t>Defense +3 for 2 turns</t>
+  </si>
+  <si>
+    <t>Deal 12 damage, Attack +2 for 1 turn</t>
+  </si>
+  <si>
+    <t>ToType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>作用对象</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -153,6 +151,19 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -196,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -208,6 +219,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -526,19 +543,19 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="51" customWidth="1"/>
-    <col min="4" max="5" width="28" customWidth="1"/>
-    <col min="6" max="7" width="17" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="7" width="17" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
     <col min="9" max="9" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,220 +569,193 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
       </c>
       <c r="E3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F3" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3"/>
+        <v>100</v>
+      </c>
+      <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="D4" s="3">
         <v>2</v>
       </c>
       <c r="E4" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
         <v>15</v>
       </c>
-      <c r="G4" s="3">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3"/>
+      <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>14</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="D5" s="3">
         <v>3</v>
       </c>
       <c r="E5" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
         <v>8</v>
       </c>
-      <c r="G5" s="3">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3"/>
+      <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="D6" s="3">
         <v>0</v>
       </c>
       <c r="E6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
       </c>
       <c r="G6" s="3">
-        <v>5</v>
-      </c>
-      <c r="H6" s="3">
-        <v>3</v>
-      </c>
-      <c r="I6" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>27</v>
+        <v>16</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="D7" s="3">
         <v>0</v>
       </c>
       <c r="E7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3">
         <v>0</v>
       </c>
       <c r="G7" s="3">
-        <v>3</v>
-      </c>
-      <c r="H7" s="3">
-        <v>2</v>
-      </c>
-      <c r="I7" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="D8" s="3">
         <v>1</v>
       </c>
       <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <v>1</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12</v>
       </c>
-      <c r="G8" s="3">
-        <v>2</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1</v>
-      </c>
-      <c r="I8" s="3"/>
+      <c r="H8" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <dataValidations count="2">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D3:D200" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"None,Attack,Hp,Defense"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E3:E200" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"None,Attack,Defense"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
